--- a/data/cox_xlsx/NORTHM.CO.xlsx
+++ b/data/cox_xlsx/NORTHM.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="477">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -898,6 +898,9 @@
   </si>
   <si>
     <t>Deferred tax</t>
+  </si>
+  <si>
+    <t>Credit institutions LT</t>
   </si>
   <si>
     <t>Accrued Interest</t>
@@ -1578,7 +1581,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1662,6 +1665,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -15167,8 +15173,8 @@
       </c>
     </row>
     <row r="109" ht="15.0" customHeight="1">
-      <c r="A109" s="14" t="s">
-        <v>275</v>
+      <c r="A109" s="28" t="s">
+        <v>293</v>
       </c>
       <c r="B109" s="15">
         <v>148.38</v>
@@ -15325,7 +15331,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B112" s="18"/>
       <c r="C112" s="18"/>
@@ -15370,7 +15376,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B113" s="18"/>
       <c r="C113" s="18"/>
@@ -15409,7 +15415,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B114" s="18"/>
       <c r="C114" s="18"/>
@@ -15450,7 +15456,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B115" s="18"/>
       <c r="C115" s="18"/>
@@ -15485,7 +15491,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B116" s="18"/>
       <c r="C116" s="18"/>
@@ -15518,7 +15524,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B117" s="18"/>
       <c r="C117" s="18"/>
@@ -15547,7 +15553,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B118" s="17">
         <v>218.3</v>
@@ -15618,7 +15624,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B119" s="17">
         <v>518.55</v>
@@ -15689,7 +15695,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B120" s="18"/>
       <c r="C120" s="18"/>
@@ -15746,7 +15752,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B121" s="18"/>
       <c r="C121" s="18"/>
@@ -15799,7 +15805,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B122" s="15">
         <v>158.66</v>
@@ -15870,7 +15876,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B123" s="21">
         <v>-1.11</v>
@@ -15937,7 +15943,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B124" s="15">
         <v>1762.07</v>
@@ -16008,7 +16014,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B125" s="18"/>
       <c r="C125" s="18"/>
@@ -16045,7 +16051,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B126" s="17">
         <v>1919.63</v>
@@ -16116,7 +16122,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B127" s="18"/>
       <c r="C127" s="18"/>
@@ -16200,7 +16206,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B129" s="19"/>
       <c r="C129" s="19"/>
@@ -16243,7 +16249,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B130" s="19"/>
       <c r="C130" s="17">
@@ -16312,7 +16318,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B131" s="18"/>
       <c r="C131" s="18"/>
@@ -16353,7 +16359,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B132" s="17">
         <v>2438.18</v>
@@ -16424,7 +16430,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B133" s="18"/>
       <c r="C133" s="20">
@@ -16493,7 +16499,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B134" s="18"/>
       <c r="C134" s="20">
@@ -16562,7 +16568,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B135" s="18"/>
       <c r="C135" s="20">
@@ -16631,7 +16637,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B136" s="18"/>
       <c r="C136" s="18"/>
@@ -16686,7 +16692,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B137" s="18"/>
       <c r="C137" s="20">
@@ -16745,7 +16751,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B138" s="18"/>
       <c r="C138" s="20">
@@ -16794,7 +16800,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B139" s="18"/>
       <c r="C139" s="15">
@@ -16853,7 +16859,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B140" s="18"/>
       <c r="C140" s="20">
@@ -16892,7 +16898,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B141" s="18"/>
       <c r="C141" s="20">
@@ -16925,7 +16931,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B142" s="18"/>
       <c r="C142" s="20">
@@ -16958,7 +16964,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B143" s="18"/>
       <c r="C143" s="18"/>
@@ -16993,7 +16999,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B144" s="18"/>
       <c r="C144" s="18"/>
@@ -17026,7 +17032,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B145" s="18"/>
       <c r="C145" s="20">
@@ -17095,7 +17101,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B146" s="18"/>
       <c r="C146" s="20">
@@ -17164,7 +17170,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B147" s="18"/>
       <c r="C147" s="20">
@@ -17233,7 +17239,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B148" s="18"/>
       <c r="C148" s="20">
@@ -18173,7 +18179,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18559,70 +18565,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -18698,7 +18704,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -18796,7 +18802,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B20" s="20">
         <v>84.85</v>
@@ -18867,7 +18873,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B21" s="15">
         <v>110.57</v>
@@ -18997,7 +19003,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="20">
@@ -19064,7 +19070,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="20">
@@ -19131,7 +19137,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -19182,7 +19188,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -19239,7 +19245,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -19294,7 +19300,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -19343,7 +19349,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -19445,7 +19451,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="20">
@@ -19476,7 +19482,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="15">
@@ -19505,7 +19511,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="22">
@@ -19540,7 +19546,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -19569,7 +19575,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
@@ -19600,7 +19606,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -19631,7 +19637,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B37" s="21">
         <v>-39.99</v>
@@ -19688,7 +19694,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -19747,7 +19753,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="21">
@@ -19814,7 +19820,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="21">
@@ -19849,7 +19855,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="18">
@@ -19880,7 +19886,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="18"/>
@@ -19947,7 +19953,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="18"/>
@@ -19988,7 +19994,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B44" s="20">
         <v>2.67</v>
@@ -20059,7 +20065,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B45" s="21">
         <v>-12.23</v>
@@ -20130,7 +20136,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B46" s="21">
         <v>-14.11</v>
@@ -20161,7 +20167,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -20194,7 +20200,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -20227,7 +20233,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
@@ -20258,7 +20264,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -20291,7 +20297,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -20324,7 +20330,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -20353,7 +20359,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B53" s="21">
         <v>-6.9</v>
@@ -20384,7 +20390,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B54" s="17">
         <v>124.84</v>
@@ -20455,7 +20461,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -20510,7 +20516,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B56" s="21">
         <v>-86.41</v>
@@ -20553,7 +20559,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
@@ -20592,7 +20598,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="18">
@@ -20631,7 +20637,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
@@ -20672,7 +20678,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -20713,7 +20719,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B61" s="20">
         <v>31.68</v>
@@ -20782,7 +20788,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B62" s="15">
         <v>247.32</v>
@@ -20841,7 +20847,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B63" s="22">
         <v>-168.28</v>
@@ -20900,7 +20906,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B64" s="20">
         <v>7.68</v>
@@ -20941,7 +20947,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B65" s="20">
         <v>3.14</v>
@@ -21008,7 +21014,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B66" s="21">
         <v>-31.84</v>
@@ -21043,7 +21049,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -21074,7 +21080,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B68" s="21">
         <v>-3.45</v>
@@ -21115,7 +21121,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
@@ -21144,7 +21150,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B70" s="18"/>
       <c r="C70" s="18"/>
@@ -21205,7 +21211,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
@@ -21248,7 +21254,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="18"/>
@@ -21283,7 +21289,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B73" s="18"/>
       <c r="C73" s="18"/>
@@ -21344,7 +21350,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
@@ -21375,7 +21381,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -21408,7 +21414,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -21445,7 +21451,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B77" s="18"/>
       <c r="C77" s="18"/>
@@ -21478,7 +21484,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B78" s="18"/>
       <c r="C78" s="18"/>
@@ -21513,7 +21519,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B79" s="20">
         <v>25.88</v>
@@ -21542,7 +21548,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B80" s="24">
         <v>25.72</v>
@@ -21613,7 +21619,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B81" s="18"/>
       <c r="C81" s="18"/>
@@ -21646,7 +21652,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B82" s="21">
         <v>-34.97</v>
@@ -21717,7 +21723,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B83" s="18">
         <v>0.0</v>
@@ -21774,7 +21780,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B84" s="18">
         <v>0.0</v>
@@ -21811,7 +21817,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -21862,7 +21868,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B86" s="18"/>
       <c r="C86" s="18"/>
@@ -21893,7 +21899,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B87" s="18"/>
       <c r="C87" s="18">
@@ -21924,7 +21930,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B88" s="18"/>
       <c r="C88" s="18"/>
@@ -21955,7 +21961,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
@@ -21992,7 +21998,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
@@ -22037,7 +22043,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
@@ -22068,7 +22074,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -22103,7 +22109,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B93" s="18"/>
       <c r="C93" s="18"/>
@@ -22132,7 +22138,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="16" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B94" s="23">
         <v>-34.97</v>
@@ -22203,7 +22209,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B95" s="18"/>
       <c r="C95" s="18"/>
@@ -22232,7 +22238,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B96" s="18"/>
       <c r="C96" s="18"/>
@@ -22263,7 +22269,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B97" s="20">
         <v>61.54</v>
@@ -22334,7 +22340,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B98" s="15">
         <v>178.12</v>
@@ -22405,7 +22411,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B99" s="17">
         <v>115.59</v>
@@ -22476,7 +22482,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
@@ -22505,7 +22511,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B101" s="18"/>
       <c r="C101" s="18"/>
@@ -22534,7 +22540,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B102" s="18"/>
       <c r="C102" s="18"/>
@@ -23480,7 +23486,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23653,31 +23659,31 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -24157,7 +24163,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -24258,3677 +24264,3677 @@
         <v>71</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>425</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>425</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="B21" s="32">
         <v>433.74</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>1032.35</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>738.03</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>1946.0</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>1456.25</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>780.13</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>692.67</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>785.15</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>216.21</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>227.79</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>355.71</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="32">
         <v>354.37</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="32">
         <v>271.24</v>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="32">
         <v>359.71</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="32">
         <v>467.45</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="32">
         <v>437.5</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="32">
         <v>554.07</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="32">
         <v>783.59</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="32">
         <v>1646.44</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="32">
         <v>1381.25</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="32">
         <v>679.53</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="32">
         <v>674.4</v>
       </c>
-      <c r="X21" s="31">
+      <c r="X21" s="32">
         <v>457.3</v>
       </c>
-      <c r="Y21" s="31">
+      <c r="Y21" s="32">
         <v>583.76</v>
       </c>
-      <c r="Z21" s="31">
+      <c r="Z21" s="32">
         <v>1242.55</v>
       </c>
-      <c r="AA21" s="31">
+      <c r="AA21" s="32">
         <v>1559.1</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="32">
         <v>1474.12</v>
       </c>
-      <c r="AC21" s="31">
+      <c r="AC21" s="32">
         <v>1099.79</v>
       </c>
-      <c r="AD21" s="31">
+      <c r="AD21" s="32">
         <v>728.39</v>
       </c>
-      <c r="AE21" s="32"/>
+      <c r="AE21" s="33"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="B22" s="32">
         <v>1251.64</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>1285.35</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>1161.18</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>1127.59</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>821.9</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>543.29</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>467.71</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>412.04</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="32">
         <v>303.09</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="32">
         <v>362.31</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="32">
         <v>407.53</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="32">
         <v>397.52</v>
       </c>
-      <c r="N22" s="31">
+      <c r="N22" s="32">
         <v>371.23</v>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="32">
         <v>488.39</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="32">
         <v>730.09</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="32">
         <v>966.62</v>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="32">
         <v>1188.84</v>
       </c>
-      <c r="S22" s="31">
+      <c r="S22" s="32">
         <v>1006.49</v>
       </c>
-      <c r="T22" s="31">
+      <c r="T22" s="32">
         <v>984.45</v>
       </c>
-      <c r="U22" s="31">
+      <c r="U22" s="32">
         <v>752.33</v>
       </c>
-      <c r="V22" s="31">
+      <c r="V22" s="32">
         <v>741.3</v>
       </c>
-      <c r="W22" s="31">
+      <c r="W22" s="32">
         <v>939.38</v>
       </c>
-      <c r="X22" s="31">
+      <c r="X22" s="32">
         <v>941.64</v>
       </c>
-      <c r="Y22" s="31">
+      <c r="Y22" s="32">
         <v>1149.09</v>
       </c>
-      <c r="Z22" s="31">
+      <c r="Z22" s="32">
         <v>1214.71</v>
       </c>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32"/>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="32"/>
-      <c r="AE22" s="32"/>
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="33"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="33"/>
+      <c r="AE22" s="33"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>427</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="29"/>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
-      <c r="AE23" s="29"/>
+      <c r="A23" s="29" t="s">
+        <v>428</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>427</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="B24" s="32">
         <v>1525.46</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>1956.1</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>1612.09</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>2916.41</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>2253.3</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>1175.96</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>891.43</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>933.84</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <v>323.68</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>363.76</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <v>443.12</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="32">
         <v>358.73</v>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="32">
         <v>337.59</v>
       </c>
-      <c r="O24" s="31">
+      <c r="O24" s="32">
         <v>475.85</v>
       </c>
-      <c r="P24" s="31">
+      <c r="P24" s="32">
         <v>524.93</v>
       </c>
-      <c r="Q24" s="31">
+      <c r="Q24" s="32">
         <v>505.17</v>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="32">
         <v>378.85</v>
       </c>
-      <c r="S24" s="31">
+      <c r="S24" s="32">
         <v>471.96</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="32">
         <v>1441.28</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="32">
         <v>1210.98</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="32">
         <v>359.02</v>
       </c>
-      <c r="W24" s="31">
+      <c r="W24" s="32">
         <v>427.44</v>
       </c>
-      <c r="X24" s="31">
+      <c r="X24" s="32">
         <v>327.46</v>
       </c>
-      <c r="Y24" s="31">
+      <c r="Y24" s="32">
         <v>477.09</v>
       </c>
-      <c r="Z24" s="31">
+      <c r="Z24" s="32">
         <v>1164.1</v>
       </c>
-      <c r="AA24" s="31">
+      <c r="AA24" s="32">
         <v>1544.78</v>
       </c>
-      <c r="AB24" s="31">
+      <c r="AB24" s="32">
         <v>1544.96</v>
       </c>
-      <c r="AC24" s="31">
+      <c r="AC24" s="32">
         <v>1198.39</v>
       </c>
-      <c r="AD24" s="31">
+      <c r="AD24" s="32">
         <v>894.8</v>
       </c>
-      <c r="AE24" s="32"/>
+      <c r="AE24" s="33"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>428</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>429</v>
+      </c>
+      <c r="B25" s="32">
         <v>2266.04</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>2132.45</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>1825.91</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>1625.63</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>1164.48</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>742.57</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>607.77</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>513.08</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>385.48</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <v>455.09</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <v>482.78</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="32">
         <v>464.28</v>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="32">
         <v>402.8</v>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="32">
         <v>446.78</v>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="32">
         <v>626.12</v>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="32">
         <v>808.0</v>
       </c>
-      <c r="R25" s="31">
+      <c r="R25" s="32">
         <v>911.91</v>
       </c>
-      <c r="S25" s="31">
+      <c r="S25" s="32">
         <v>762.59</v>
       </c>
-      <c r="T25" s="31">
+      <c r="T25" s="32">
         <v>766.86</v>
       </c>
-      <c r="U25" s="31">
+      <c r="U25" s="32">
         <v>559.71</v>
       </c>
-      <c r="V25" s="31">
+      <c r="V25" s="32">
         <v>561.49</v>
       </c>
-      <c r="W25" s="31">
+      <c r="W25" s="32">
         <v>818.78</v>
       </c>
-      <c r="X25" s="31">
+      <c r="X25" s="32">
         <v>891.33</v>
       </c>
-      <c r="Y25" s="31">
+      <c r="Y25" s="32">
         <v>1142.11</v>
       </c>
-      <c r="Z25" s="31">
+      <c r="Z25" s="32">
         <v>1263.28</v>
       </c>
-      <c r="AA25" s="32"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="32"/>
-      <c r="AE25" s="32"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="33"/>
+      <c r="AD25" s="33"/>
+      <c r="AE25" s="33"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>429</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>430</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>430</v>
-      </c>
-      <c r="B27" s="33">
+      <c r="A27" s="31" t="s">
+        <v>431</v>
+      </c>
+      <c r="B27" s="34">
         <v>76.06</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <v>97.54</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <v>80.38</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>145.42</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>112.36</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>58.64</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>44.45</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="34">
         <v>46.56</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <v>16.14</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <v>18.14</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <v>22.1</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>17.89</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="34">
         <v>16.83</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <v>23.73</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="34">
         <v>26.17</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="34">
         <v>25.19</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="34">
         <v>17.0</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>21.18</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="34">
         <v>64.69</v>
       </c>
-      <c r="U27" s="33">
+      <c r="U27" s="34">
         <v>54.35</v>
       </c>
-      <c r="V27" s="33">
+      <c r="V27" s="34">
         <v>16.11</v>
       </c>
-      <c r="W27" s="33">
+      <c r="W27" s="34">
         <v>19.18</v>
       </c>
-      <c r="X27" s="33">
+      <c r="X27" s="34">
         <v>14.7</v>
       </c>
-      <c r="Y27" s="33">
+      <c r="Y27" s="34">
         <v>21.41</v>
       </c>
-      <c r="Z27" s="33">
+      <c r="Z27" s="34">
         <v>52.25</v>
       </c>
-      <c r="AA27" s="33">
+      <c r="AA27" s="34">
         <v>77.24</v>
       </c>
-      <c r="AB27" s="33">
+      <c r="AB27" s="34">
         <v>77.25</v>
       </c>
-      <c r="AC27" s="33">
+      <c r="AC27" s="34">
         <v>59.92</v>
       </c>
-      <c r="AD27" s="33">
+      <c r="AD27" s="34">
         <v>44.74</v>
       </c>
-      <c r="AE27" s="32"/>
+      <c r="AE27" s="33"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="B28" s="31">
+      <c r="A28" s="31" t="s">
+        <v>432</v>
+      </c>
+      <c r="B28" s="32">
         <v>112.99</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>106.33</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <v>91.04</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <v>81.06</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <v>58.06</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <v>37.03</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <v>30.31</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="34">
         <v>25.58</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>19.22</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>22.69</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>24.07</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>23.15</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="34">
         <v>19.8</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <v>21.52</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="34">
         <v>29.1</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="34">
         <v>36.77</v>
       </c>
-      <c r="R28" s="33">
+      <c r="R28" s="34">
         <v>40.93</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="34">
         <v>34.23</v>
       </c>
-      <c r="T28" s="33">
+      <c r="T28" s="34">
         <v>34.42</v>
       </c>
-      <c r="U28" s="33">
+      <c r="U28" s="34">
         <v>25.12</v>
       </c>
-      <c r="V28" s="33">
+      <c r="V28" s="34">
         <v>25.2</v>
       </c>
-      <c r="W28" s="33">
+      <c r="W28" s="34">
         <v>38.39</v>
       </c>
-      <c r="X28" s="33">
+      <c r="X28" s="34">
         <v>42.73</v>
       </c>
-      <c r="Y28" s="33">
+      <c r="Y28" s="34">
         <v>55.46</v>
       </c>
-      <c r="Z28" s="33">
+      <c r="Z28" s="34">
         <v>61.97</v>
       </c>
-      <c r="AA28" s="32"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="32"/>
-      <c r="AE28" s="32"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
+      <c r="AC28" s="33"/>
+      <c r="AD28" s="33"/>
+      <c r="AE28" s="33"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>432</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="29"/>
+      <c r="A29" s="29" t="s">
+        <v>433</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="B30" s="34">
+      <c r="A30" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="B30" s="35">
         <v>-1.85</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="36">
         <v>28.67</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>16.6</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="36">
         <v>6.6</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>13.56</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>14.06</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="36">
         <v>13.15</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="35">
         <v>-0.76</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>-7.78</v>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="36">
         <v>10.03</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="36">
         <v>17.02</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="36">
         <v>18.35</v>
       </c>
-      <c r="N30" s="35">
+      <c r="N30" s="36">
         <v>19.46</v>
       </c>
-      <c r="O30" s="35">
+      <c r="O30" s="36">
         <v>31.02</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="36">
         <v>27.35</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="36">
         <v>10.92</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="36">
         <v>2.63</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>-4.04</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="36">
         <v>6.34</v>
       </c>
-      <c r="U30" s="35">
+      <c r="U30" s="36">
         <v>9.42</v>
       </c>
-      <c r="V30" s="34">
+      <c r="V30" s="35">
         <v>-30.22</v>
       </c>
-      <c r="W30" s="34">
+      <c r="W30" s="35">
         <v>-46.37</v>
       </c>
-      <c r="X30" s="34">
+      <c r="X30" s="35">
         <v>-12.74</v>
       </c>
-      <c r="Y30" s="34">
+      <c r="Y30" s="35">
         <v>-4.35</v>
       </c>
-      <c r="Z30" s="35">
+      <c r="Z30" s="36">
         <v>7.71</v>
       </c>
-      <c r="AA30" s="35">
+      <c r="AA30" s="36">
         <v>1.84</v>
       </c>
-      <c r="AB30" s="34">
+      <c r="AB30" s="35">
         <v>-0.78</v>
       </c>
-      <c r="AC30" s="34">
+      <c r="AC30" s="35">
         <v>-1.4</v>
       </c>
-      <c r="AD30" s="35">
+      <c r="AD30" s="36">
         <v>19.02</v>
       </c>
-      <c r="AE30" s="35"/>
+      <c r="AE30" s="36"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>434</v>
-      </c>
-      <c r="B31" s="35">
+      <c r="A31" s="31" t="s">
+        <v>435</v>
+      </c>
+      <c r="B31" s="36">
         <v>12.61</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <v>14.76</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="36">
         <v>11.79</v>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="36">
         <v>9.41</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="36">
         <v>9.79</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="36">
         <v>7.67</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="36">
         <v>6.67</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="36">
         <v>6.36</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="36">
         <v>12.4</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="36">
         <v>20.23</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="36">
         <v>23.48</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="36">
         <v>21.88</v>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="36">
         <v>19.95</v>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="36">
         <v>15.41</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="36">
         <v>9.03</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="36">
         <v>6.37</v>
       </c>
-      <c r="R31" s="35">
+      <c r="R31" s="36">
         <v>2.32</v>
       </c>
-      <c r="S31" s="34">
+      <c r="S31" s="35">
         <v>-2.86</v>
       </c>
-      <c r="T31" s="34">
+      <c r="T31" s="35">
         <v>-3.66</v>
       </c>
-      <c r="U31" s="34">
+      <c r="U31" s="35">
         <v>-8.77</v>
       </c>
-      <c r="V31" s="34">
+      <c r="V31" s="35">
         <v>-10.06</v>
       </c>
-      <c r="W31" s="34">
+      <c r="W31" s="35">
         <v>-3.36</v>
       </c>
-      <c r="X31" s="35">
+      <c r="X31" s="36">
         <v>0.76</v>
       </c>
-      <c r="Y31" s="35">
+      <c r="Y31" s="36">
         <v>1.08</v>
       </c>
-      <c r="Z31" s="35">
+      <c r="Z31" s="36">
         <v>4.09</v>
       </c>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="35"/>
-      <c r="AC31" s="35"/>
-      <c r="AD31" s="35"/>
-      <c r="AE31" s="35"/>
+      <c r="AA31" s="36"/>
+      <c r="AB31" s="36"/>
+      <c r="AC31" s="36"/>
+      <c r="AD31" s="36"/>
+      <c r="AE31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>435</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="29"/>
-      <c r="AE32" s="29"/>
+      <c r="A32" s="29" t="s">
+        <v>436</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B33" s="35">
+      <c r="A33" s="31" t="s">
+        <v>437</v>
+      </c>
+      <c r="B33" s="36">
         <v>8.3</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <v>6.15</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>8.77</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <v>4.63</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <v>5.01</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <v>6.74</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>4.48</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <v>0.0</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <v>0.0</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="36">
         <v>0.0</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="36">
         <v>0.0</v>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="36">
         <v>0.0</v>
       </c>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35">
+      <c r="N33" s="36"/>
+      <c r="O33" s="36">
         <v>0.0</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="36">
         <v>11.5</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="36">
         <v>7.97</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="36">
         <v>0.0</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="36">
         <v>3.62</v>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="36">
         <v>0.98</v>
       </c>
-      <c r="U33" s="35">
+      <c r="U33" s="36">
         <v>0.0</v>
       </c>
-      <c r="V33" s="35">
+      <c r="V33" s="36">
         <v>0.0</v>
       </c>
-      <c r="W33" s="35">
+      <c r="W33" s="36">
         <v>0.0</v>
       </c>
-      <c r="X33" s="35">
+      <c r="X33" s="36">
         <v>0.0</v>
       </c>
-      <c r="Y33" s="35">
+      <c r="Y33" s="36">
         <v>3.24</v>
       </c>
-      <c r="Z33" s="35">
+      <c r="Z33" s="36">
         <v>1.43</v>
       </c>
-      <c r="AA33" s="35">
+      <c r="AA33" s="36">
         <v>0.95</v>
       </c>
-      <c r="AB33" s="35">
+      <c r="AB33" s="36">
         <v>0.87</v>
       </c>
-      <c r="AC33" s="35">
+      <c r="AC33" s="36">
         <v>0.81</v>
       </c>
-      <c r="AD33" s="35">
+      <c r="AD33" s="36">
         <v>0.47</v>
       </c>
-      <c r="AE33" s="35"/>
+      <c r="AE33" s="36"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>437</v>
-      </c>
-      <c r="B34" s="35">
+      <c r="A34" s="31" t="s">
+        <v>438</v>
+      </c>
+      <c r="B34" s="36">
         <v>6.15</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="36">
         <v>5.93</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>5.73</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="36">
         <v>4.49</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="36">
         <v>4.12</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="36">
         <v>3.2</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="36">
         <v>1.31</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="36">
         <v>0.0</v>
       </c>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35"/>
-      <c r="O34" s="35">
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36">
         <v>5.22</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="36">
         <v>4.29</v>
       </c>
-      <c r="Q34" s="35">
+      <c r="Q34" s="36">
         <v>1.88</v>
       </c>
-      <c r="R34" s="35">
+      <c r="R34" s="36">
         <v>0.83</v>
       </c>
-      <c r="S34" s="35">
+      <c r="S34" s="36">
         <v>0.81</v>
       </c>
-      <c r="T34" s="35">
+      <c r="T34" s="36">
         <v>0.37</v>
       </c>
-      <c r="U34" s="35">
+      <c r="U34" s="36">
         <v>0.55</v>
       </c>
-      <c r="V34" s="35">
+      <c r="V34" s="36">
         <v>1.16</v>
       </c>
-      <c r="W34" s="35">
+      <c r="W34" s="36">
         <v>1.17</v>
       </c>
-      <c r="X34" s="35">
+      <c r="X34" s="36">
         <v>1.17</v>
       </c>
-      <c r="Y34" s="35">
+      <c r="Y34" s="36">
         <v>1.16</v>
       </c>
-      <c r="Z34" s="35">
+      <c r="Z34" s="36">
         <v>0.91</v>
       </c>
-      <c r="AA34" s="35"/>
-      <c r="AB34" s="35"/>
-      <c r="AC34" s="35"/>
-      <c r="AD34" s="35"/>
-      <c r="AE34" s="35"/>
+      <c r="AA34" s="36"/>
+      <c r="AB34" s="36"/>
+      <c r="AC34" s="36"/>
+      <c r="AD34" s="36"/>
+      <c r="AE34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="B35" s="35">
+      <c r="A35" s="31" t="s">
+        <v>439</v>
+      </c>
+      <c r="B35" s="36">
         <v>8.3</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="36">
         <v>6.15</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="36">
         <v>8.77</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="36">
         <v>4.63</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="36">
         <v>5.01</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <v>6.74</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="36">
         <v>4.48</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <v>0.0</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <v>0.0</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="36">
         <v>0.0</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <v>0.0</v>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="36">
         <v>0.0</v>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="36">
         <v>17.54</v>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="36">
         <v>0.0</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="36">
         <v>15.97</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="36">
         <v>11.06</v>
       </c>
-      <c r="R35" s="35">
+      <c r="R35" s="36">
         <v>0.0</v>
       </c>
-      <c r="S35" s="35">
+      <c r="S35" s="36">
         <v>5.02</v>
       </c>
-      <c r="T35" s="35">
+      <c r="T35" s="36">
         <v>1.36</v>
       </c>
-      <c r="U35" s="35">
+      <c r="U35" s="36">
         <v>0.0</v>
       </c>
-      <c r="V35" s="35">
+      <c r="V35" s="36">
         <v>0.0</v>
       </c>
-      <c r="W35" s="35">
+      <c r="W35" s="36">
         <v>0.0</v>
       </c>
-      <c r="X35" s="35">
+      <c r="X35" s="36">
         <v>0.0</v>
       </c>
-      <c r="Y35" s="35">
+      <c r="Y35" s="36">
         <v>4.51</v>
       </c>
-      <c r="Z35" s="35">
+      <c r="Z35" s="36">
         <v>1.91</v>
       </c>
-      <c r="AA35" s="35">
+      <c r="AA35" s="36">
         <v>1.26</v>
       </c>
-      <c r="AB35" s="35">
+      <c r="AB35" s="36">
         <v>1.16</v>
       </c>
-      <c r="AC35" s="35">
+      <c r="AC35" s="36">
         <v>1.08</v>
       </c>
-      <c r="AD35" s="35">
+      <c r="AD35" s="36">
         <v>0.62</v>
       </c>
-      <c r="AE35" s="35"/>
+      <c r="AE35" s="36"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>439</v>
-      </c>
-      <c r="B36" s="35">
+      <c r="A36" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="B36" s="36">
         <v>6.15</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <v>5.93</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="36">
         <v>5.73</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="36">
         <v>4.49</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="36">
         <v>4.12</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <v>3.2</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="36">
         <v>1.31</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <v>0.0</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="36">
         <v>3.82</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="36">
         <v>3.4</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="36">
         <v>7.06</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="36">
         <v>9.18</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="36">
         <v>9.45</v>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="36">
         <v>7.25</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="36">
         <v>5.96</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="36">
         <v>2.61</v>
       </c>
-      <c r="R36" s="35">
+      <c r="R36" s="36">
         <v>1.15</v>
       </c>
-      <c r="S36" s="35">
+      <c r="S36" s="36">
         <v>1.12</v>
       </c>
-      <c r="T36" s="35">
+      <c r="T36" s="36">
         <v>0.51</v>
       </c>
-      <c r="U36" s="35">
+      <c r="U36" s="36">
         <v>0.77</v>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="36">
         <v>1.58</v>
       </c>
-      <c r="W36" s="35">
+      <c r="W36" s="36">
         <v>1.58</v>
       </c>
-      <c r="X36" s="35">
+      <c r="X36" s="36">
         <v>1.58</v>
       </c>
-      <c r="Y36" s="35">
+      <c r="Y36" s="36">
         <v>1.57</v>
       </c>
-      <c r="Z36" s="35">
+      <c r="Z36" s="36">
         <v>1.22</v>
       </c>
-      <c r="AA36" s="35"/>
-      <c r="AB36" s="35"/>
-      <c r="AC36" s="35"/>
-      <c r="AD36" s="35"/>
-      <c r="AE36" s="35"/>
+      <c r="AA36" s="36"/>
+      <c r="AB36" s="36"/>
+      <c r="AC36" s="36"/>
+      <c r="AD36" s="36"/>
+      <c r="AE36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>440</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
-      <c r="Z37" s="29"/>
-      <c r="AA37" s="29"/>
-      <c r="AB37" s="29"/>
-      <c r="AC37" s="29"/>
-      <c r="AD37" s="29"/>
-      <c r="AE37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>441</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>441</v>
-      </c>
-      <c r="B38" s="33">
+      <c r="A38" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="B38" s="34">
         <v>0.76</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="34">
         <v>1.01</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="34">
         <v>1.06</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="34">
         <v>1.81</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="34">
         <v>1.63</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="34">
         <v>1.22</v>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="34">
         <v>1.18</v>
       </c>
-      <c r="I38" s="33">
+      <c r="I38" s="34">
         <v>1.33</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="34">
         <v>0.53</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="34">
         <v>0.5</v>
       </c>
-      <c r="L38" s="33">
+      <c r="L38" s="34">
         <v>0.64</v>
       </c>
-      <c r="M38" s="33">
+      <c r="M38" s="34">
         <v>0.59</v>
       </c>
-      <c r="N38" s="33">
+      <c r="N38" s="34">
         <v>0.64</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="34">
         <v>0.88</v>
       </c>
-      <c r="P38" s="33">
+      <c r="P38" s="34">
         <v>0.98</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="Q38" s="34">
         <v>0.79</v>
       </c>
-      <c r="R38" s="33">
+      <c r="R38" s="34">
         <v>0.4</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S38" s="34">
         <v>0.84</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="34">
         <v>2.44</v>
       </c>
-      <c r="U38" s="33">
+      <c r="U38" s="34">
         <v>3.24</v>
       </c>
-      <c r="V38" s="33">
+      <c r="V38" s="34">
         <v>1.32</v>
       </c>
-      <c r="W38" s="33">
+      <c r="W38" s="34">
         <v>1.75</v>
       </c>
-      <c r="X38" s="33">
+      <c r="X38" s="34">
         <v>1.9</v>
       </c>
-      <c r="Y38" s="33">
+      <c r="Y38" s="34">
         <v>3.01</v>
       </c>
-      <c r="Z38" s="33">
+      <c r="Z38" s="34">
         <v>4.68</v>
       </c>
-      <c r="AA38" s="33">
+      <c r="AA38" s="34">
         <v>7.62</v>
       </c>
-      <c r="AB38" s="33">
+      <c r="AB38" s="34">
         <v>5.8</v>
       </c>
-      <c r="AC38" s="33">
+      <c r="AC38" s="34">
         <v>5.86</v>
       </c>
-      <c r="AD38" s="33">
+      <c r="AD38" s="34">
         <v>4.64</v>
       </c>
-      <c r="AE38" s="32"/>
+      <c r="AE38" s="33"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="B39" s="33">
+      <c r="A39" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="B39" s="34">
         <v>1.23</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <v>1.35</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="34">
         <v>1.42</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="34">
         <v>1.51</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="34">
         <v>1.25</v>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <v>0.98</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <v>0.84</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="34">
         <v>0.72</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="34">
         <v>0.58</v>
       </c>
-      <c r="K39" s="33">
+      <c r="K39" s="34">
         <v>0.65</v>
       </c>
-      <c r="L39" s="33">
+      <c r="L39" s="34">
         <v>0.74</v>
       </c>
-      <c r="M39" s="33">
+      <c r="M39" s="34">
         <v>0.77</v>
       </c>
-      <c r="N39" s="33">
+      <c r="N39" s="34">
         <v>0.72</v>
       </c>
-      <c r="O39" s="33">
+      <c r="O39" s="34">
         <v>0.76</v>
       </c>
-      <c r="P39" s="33">
+      <c r="P39" s="34">
         <v>1.03</v>
       </c>
-      <c r="Q39" s="33">
+      <c r="Q39" s="34">
         <v>1.32</v>
       </c>
-      <c r="R39" s="33">
+      <c r="R39" s="34">
         <v>1.46</v>
       </c>
-      <c r="S39" s="33">
+      <c r="S39" s="34">
         <v>1.91</v>
       </c>
-      <c r="T39" s="33">
+      <c r="T39" s="34">
         <v>2.28</v>
       </c>
-      <c r="U39" s="33">
+      <c r="U39" s="34">
         <v>2.3</v>
       </c>
-      <c r="V39" s="33">
+      <c r="V39" s="34">
         <v>2.5</v>
       </c>
-      <c r="W39" s="33">
+      <c r="W39" s="34">
         <v>3.9</v>
       </c>
-      <c r="X39" s="33">
+      <c r="X39" s="34">
         <v>4.83</v>
       </c>
-      <c r="Y39" s="33">
+      <c r="Y39" s="34">
         <v>5.54</v>
       </c>
-      <c r="Z39" s="33">
+      <c r="Z39" s="34">
         <v>5.72</v>
       </c>
-      <c r="AA39" s="32"/>
-      <c r="AB39" s="32"/>
-      <c r="AC39" s="32"/>
-      <c r="AD39" s="32"/>
-      <c r="AE39" s="32"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
+      <c r="AC39" s="33"/>
+      <c r="AD39" s="33"/>
+      <c r="AE39" s="33"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>443</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="AD40" s="29"/>
-      <c r="AE40" s="29"/>
+      <c r="A40" s="29" t="s">
+        <v>444</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
+      <c r="AE40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="B41" s="33">
+      <c r="A41" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="B41" s="34">
         <v>0.88</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="34">
         <v>1.42</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="34">
         <v>1.11</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="34">
         <v>1.9</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="34">
         <v>1.74</v>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <v>1.33</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="34">
         <v>1.31</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="34">
         <v>1.5</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="34">
         <v>0.6</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="34">
         <v>0.65</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="34">
         <v>0.87</v>
       </c>
-      <c r="M41" s="33">
+      <c r="M41" s="34">
         <v>0.91</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="34">
         <v>0.8</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="34">
         <v>1.0</v>
       </c>
-      <c r="P41" s="33">
+      <c r="P41" s="34">
         <v>0.85</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="Q41" s="34">
         <v>0.8</v>
       </c>
-      <c r="R41" s="33">
+      <c r="R41" s="34">
         <v>0.36</v>
       </c>
-      <c r="S41" s="33">
+      <c r="S41" s="34">
         <v>0.88</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="34">
         <v>3.79</v>
       </c>
-      <c r="U41" s="33">
+      <c r="U41" s="34">
         <v>6.64</v>
       </c>
-      <c r="V41" s="33">
+      <c r="V41" s="34">
         <v>2.04</v>
       </c>
-      <c r="W41" s="33">
+      <c r="W41" s="34">
         <v>2.62</v>
       </c>
-      <c r="X41" s="33">
+      <c r="X41" s="34">
         <v>2.78</v>
       </c>
-      <c r="Y41" s="33">
+      <c r="Y41" s="34">
         <v>3.57</v>
       </c>
-      <c r="Z41" s="33">
+      <c r="Z41" s="34">
         <v>5.35</v>
       </c>
-      <c r="AA41" s="33">
+      <c r="AA41" s="34">
         <v>7.73</v>
       </c>
-      <c r="AB41" s="33">
+      <c r="AB41" s="34">
         <v>5.88</v>
       </c>
-      <c r="AC41" s="33">
+      <c r="AC41" s="34">
         <v>5.86</v>
       </c>
-      <c r="AD41" s="33">
+      <c r="AD41" s="34">
         <v>4.64</v>
       </c>
-      <c r="AE41" s="32"/>
+      <c r="AE41" s="33"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>445</v>
-      </c>
-      <c r="B42" s="33">
+      <c r="A42" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="B42" s="34">
         <v>1.41</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <v>1.52</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="34">
         <v>1.52</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="34">
         <v>1.63</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="34">
         <v>1.37</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <v>1.11</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="34">
         <v>1.01</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="34">
         <v>0.92</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="34">
         <v>0.76</v>
       </c>
-      <c r="K42" s="33">
+      <c r="K42" s="34">
         <v>0.84</v>
       </c>
-      <c r="L42" s="33">
+      <c r="L42" s="34">
         <v>0.88</v>
       </c>
-      <c r="M42" s="33">
+      <c r="M42" s="34">
         <v>0.87</v>
       </c>
-      <c r="N42" s="33">
+      <c r="N42" s="34">
         <v>0.73</v>
       </c>
-      <c r="O42" s="33">
+      <c r="O42" s="34">
         <v>0.74</v>
       </c>
-      <c r="P42" s="33">
+      <c r="P42" s="34">
         <v>1.06</v>
       </c>
-      <c r="Q42" s="33">
+      <c r="Q42" s="34">
         <v>1.5</v>
       </c>
-      <c r="R42" s="33">
+      <c r="R42" s="34">
         <v>1.77</v>
       </c>
-      <c r="S42" s="33">
+      <c r="S42" s="34">
         <v>2.71</v>
       </c>
-      <c r="T42" s="33">
+      <c r="T42" s="34">
         <v>3.7</v>
       </c>
-      <c r="U42" s="33">
+      <c r="U42" s="34">
         <v>3.64</v>
       </c>
-      <c r="V42" s="33">
+      <c r="V42" s="34">
         <v>3.4</v>
       </c>
-      <c r="W42" s="33">
+      <c r="W42" s="34">
         <v>4.8</v>
       </c>
-      <c r="X42" s="33">
+      <c r="X42" s="34">
         <v>5.45</v>
       </c>
-      <c r="Y42" s="33">
+      <c r="Y42" s="34">
         <v>5.87</v>
       </c>
-      <c r="Z42" s="33">
+      <c r="Z42" s="34">
         <v>5.91</v>
       </c>
-      <c r="AA42" s="32"/>
-      <c r="AB42" s="32"/>
-      <c r="AC42" s="32"/>
-      <c r="AD42" s="32"/>
-      <c r="AE42" s="32"/>
+      <c r="AA42" s="33"/>
+      <c r="AB42" s="33"/>
+      <c r="AC42" s="33"/>
+      <c r="AD42" s="33"/>
+      <c r="AE42" s="33"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>446</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
-      <c r="AA43" s="29"/>
-      <c r="AB43" s="29"/>
-      <c r="AC43" s="29"/>
-      <c r="AD43" s="29"/>
-      <c r="AE43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>447</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
+      <c r="AE43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>447</v>
-      </c>
-      <c r="B44" s="33">
+      <c r="A44" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B44" s="34">
         <v>0.67</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="34">
         <v>1.27</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="34">
         <v>1.06</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="34">
         <v>1.94</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="34">
         <v>1.42</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <v>0.79</v>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="34">
         <v>0.56</v>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="34">
         <v>0.74</v>
       </c>
-      <c r="J44" s="33">
+      <c r="J44" s="34">
         <v>0.28</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="34">
         <v>0.26</v>
       </c>
-      <c r="L44" s="33">
+      <c r="L44" s="34">
         <v>0.32</v>
       </c>
-      <c r="M44" s="33">
+      <c r="M44" s="34">
         <v>0.28</v>
       </c>
-      <c r="N44" s="33">
+      <c r="N44" s="34">
         <v>0.3</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="34">
         <v>0.37</v>
       </c>
-      <c r="P44" s="33">
+      <c r="P44" s="34">
         <v>0.44</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="Q44" s="34">
         <v>0.45</v>
       </c>
-      <c r="R44" s="33">
+      <c r="R44" s="34">
         <v>0.23</v>
       </c>
-      <c r="S44" s="33">
+      <c r="S44" s="34">
         <v>0.29</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="34">
         <v>0.74</v>
       </c>
-      <c r="U44" s="33">
+      <c r="U44" s="34">
         <v>0.75</v>
       </c>
-      <c r="V44" s="33">
+      <c r="V44" s="34">
         <v>0.24</v>
       </c>
-      <c r="W44" s="33">
+      <c r="W44" s="34">
         <v>0.28</v>
       </c>
-      <c r="X44" s="33">
+      <c r="X44" s="34">
         <v>0.3</v>
       </c>
-      <c r="Y44" s="33">
+      <c r="Y44" s="34">
         <v>0.42</v>
       </c>
-      <c r="Z44" s="33">
+      <c r="Z44" s="34">
         <v>0.93</v>
       </c>
-      <c r="AA44" s="33">
+      <c r="AA44" s="34">
         <v>1.69</v>
       </c>
-      <c r="AB44" s="33">
+      <c r="AB44" s="34">
         <v>1.66</v>
       </c>
-      <c r="AC44" s="33">
+      <c r="AC44" s="34">
         <v>1.67</v>
       </c>
-      <c r="AD44" s="33">
+      <c r="AD44" s="34">
         <v>1.8</v>
       </c>
-      <c r="AE44" s="32"/>
+      <c r="AE44" s="33"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>448</v>
-      </c>
-      <c r="B45" s="33">
+      <c r="A45" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="B45" s="34">
         <v>1.24</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="34">
         <v>1.3</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="34">
         <v>1.14</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="34">
         <v>1.09</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="34">
         <v>0.77</v>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="34">
         <v>0.53</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="34">
         <v>0.43</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="34">
         <v>0.37</v>
       </c>
-      <c r="J45" s="33">
+      <c r="J45" s="34">
         <v>0.29</v>
       </c>
-      <c r="K45" s="33">
+      <c r="K45" s="34">
         <v>0.3</v>
       </c>
-      <c r="L45" s="33">
+      <c r="L45" s="34">
         <v>0.34</v>
       </c>
-      <c r="M45" s="33">
+      <c r="M45" s="34">
         <v>0.36</v>
       </c>
-      <c r="N45" s="33">
+      <c r="N45" s="34">
         <v>0.35</v>
       </c>
-      <c r="O45" s="33">
+      <c r="O45" s="34">
         <v>0.35</v>
       </c>
-      <c r="P45" s="33">
+      <c r="P45" s="34">
         <v>0.45</v>
       </c>
-      <c r="Q45" s="33">
+      <c r="Q45" s="34">
         <v>0.51</v>
       </c>
-      <c r="R45" s="33">
+      <c r="R45" s="34">
         <v>0.47</v>
       </c>
-      <c r="S45" s="33">
+      <c r="S45" s="34">
         <v>0.48</v>
       </c>
-      <c r="T45" s="33">
+      <c r="T45" s="34">
         <v>0.49</v>
       </c>
-      <c r="U45" s="33">
+      <c r="U45" s="34">
         <v>0.41</v>
       </c>
-      <c r="V45" s="33">
+      <c r="V45" s="34">
         <v>0.42</v>
       </c>
-      <c r="W45" s="33">
+      <c r="W45" s="34">
         <v>0.68</v>
       </c>
-      <c r="X45" s="33">
+      <c r="X45" s="34">
         <v>0.96</v>
       </c>
-      <c r="Y45" s="33">
+      <c r="Y45" s="34">
         <v>1.22</v>
       </c>
-      <c r="Z45" s="33">
+      <c r="Z45" s="34">
         <v>1.49</v>
       </c>
-      <c r="AA45" s="32"/>
-      <c r="AB45" s="32"/>
-      <c r="AC45" s="32"/>
-      <c r="AD45" s="32"/>
-      <c r="AE45" s="32"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="33"/>
+      <c r="AC45" s="33"/>
+      <c r="AD45" s="33"/>
+      <c r="AE45" s="33"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>449</v>
-      </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
-      <c r="AA46" s="29"/>
-      <c r="AB46" s="29"/>
-      <c r="AC46" s="29"/>
-      <c r="AD46" s="29"/>
-      <c r="AE46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>450</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
+      <c r="AE46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>450</v>
-      </c>
-      <c r="B47" s="32"/>
-      <c r="C47" s="33">
+      <c r="A47" s="31" t="s">
+        <v>451</v>
+      </c>
+      <c r="B47" s="33"/>
+      <c r="C47" s="34">
         <v>3.49</v>
       </c>
-      <c r="D47" s="33">
+      <c r="D47" s="34">
         <v>6.03</v>
       </c>
-      <c r="E47" s="33">
+      <c r="E47" s="34">
         <v>15.16</v>
       </c>
-      <c r="F47" s="33">
+      <c r="F47" s="34">
         <v>7.38</v>
       </c>
-      <c r="G47" s="33">
+      <c r="G47" s="34">
         <v>7.11</v>
       </c>
-      <c r="H47" s="33">
+      <c r="H47" s="34">
         <v>7.6</v>
       </c>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="33">
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="34">
         <v>9.97</v>
       </c>
-      <c r="L47" s="33">
+      <c r="L47" s="34">
         <v>5.88</v>
       </c>
-      <c r="M47" s="33">
+      <c r="M47" s="34">
         <v>5.45</v>
       </c>
-      <c r="N47" s="33">
+      <c r="N47" s="34">
         <v>5.14</v>
       </c>
-      <c r="O47" s="33">
+      <c r="O47" s="34">
         <v>3.22</v>
       </c>
-      <c r="P47" s="33">
+      <c r="P47" s="34">
         <v>3.66</v>
       </c>
-      <c r="Q47" s="33">
+      <c r="Q47" s="34">
         <v>9.15</v>
       </c>
-      <c r="R47" s="33">
+      <c r="R47" s="34">
         <v>37.97</v>
       </c>
-      <c r="S47" s="32"/>
-      <c r="T47" s="33">
+      <c r="S47" s="33"/>
+      <c r="T47" s="34">
         <v>15.77</v>
       </c>
-      <c r="U47" s="33">
+      <c r="U47" s="34">
         <v>10.62</v>
       </c>
-      <c r="V47" s="32"/>
-      <c r="W47" s="32"/>
-      <c r="X47" s="32"/>
-      <c r="Y47" s="32"/>
-      <c r="Z47" s="33">
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="33"/>
+      <c r="Y47" s="33"/>
+      <c r="Z47" s="34">
         <v>12.97</v>
       </c>
-      <c r="AA47" s="33">
+      <c r="AA47" s="34">
         <v>54.35</v>
       </c>
-      <c r="AB47" s="32"/>
-      <c r="AC47" s="32"/>
-      <c r="AD47" s="33">
+      <c r="AB47" s="33"/>
+      <c r="AC47" s="33"/>
+      <c r="AD47" s="34">
         <v>5.26</v>
       </c>
-      <c r="AE47" s="32"/>
+      <c r="AE47" s="33"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
-        <v>451</v>
-      </c>
-      <c r="B48" s="33">
+      <c r="A48" s="31" t="s">
+        <v>452</v>
+      </c>
+      <c r="B48" s="34">
         <v>7.93</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="34">
         <v>6.77</v>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="34">
         <v>8.48</v>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="34">
         <v>10.62</v>
       </c>
-      <c r="F48" s="33">
+      <c r="F48" s="34">
         <v>10.22</v>
       </c>
-      <c r="G48" s="33">
+      <c r="G48" s="34">
         <v>13.03</v>
       </c>
-      <c r="H48" s="33">
+      <c r="H48" s="34">
         <v>14.99</v>
       </c>
-      <c r="I48" s="33">
+      <c r="I48" s="34">
         <v>15.72</v>
       </c>
-      <c r="J48" s="33">
+      <c r="J48" s="34">
         <v>8.06</v>
       </c>
-      <c r="K48" s="33">
+      <c r="K48" s="34">
         <v>4.94</v>
       </c>
-      <c r="L48" s="33">
+      <c r="L48" s="34">
         <v>4.26</v>
       </c>
-      <c r="M48" s="33">
+      <c r="M48" s="34">
         <v>4.57</v>
       </c>
-      <c r="N48" s="33">
+      <c r="N48" s="34">
         <v>5.01</v>
       </c>
-      <c r="O48" s="33">
+      <c r="O48" s="34">
         <v>6.49</v>
       </c>
-      <c r="P48" s="33">
+      <c r="P48" s="34">
         <v>11.07</v>
       </c>
-      <c r="Q48" s="33">
+      <c r="Q48" s="34">
         <v>15.7</v>
       </c>
-      <c r="R48" s="33">
+      <c r="R48" s="34">
         <v>43.04</v>
       </c>
-      <c r="S48" s="32"/>
-      <c r="T48" s="32"/>
-      <c r="U48" s="32"/>
-      <c r="V48" s="32"/>
-      <c r="W48" s="32"/>
-      <c r="X48" s="31">
+      <c r="S48" s="33"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="33"/>
+      <c r="V48" s="33"/>
+      <c r="W48" s="33"/>
+      <c r="X48" s="32">
         <v>131.22</v>
       </c>
-      <c r="Y48" s="33">
+      <c r="Y48" s="34">
         <v>92.69</v>
       </c>
-      <c r="Z48" s="33">
+      <c r="Z48" s="34">
         <v>24.43</v>
       </c>
-      <c r="AA48" s="32"/>
-      <c r="AB48" s="32"/>
-      <c r="AC48" s="32"/>
-      <c r="AD48" s="32"/>
-      <c r="AE48" s="32"/>
+      <c r="AA48" s="33"/>
+      <c r="AB48" s="33"/>
+      <c r="AC48" s="33"/>
+      <c r="AD48" s="33"/>
+      <c r="AE48" s="33"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
-      <c r="AA49" s="29"/>
-      <c r="AB49" s="29"/>
-      <c r="AC49" s="29"/>
-      <c r="AD49" s="29"/>
-      <c r="AE49" s="29"/>
+      <c r="A49" s="29" t="s">
+        <v>453</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
+      <c r="AE49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>453</v>
-      </c>
-      <c r="B50" s="33">
+      <c r="A50" s="31" t="s">
+        <v>454</v>
+      </c>
+      <c r="B50" s="34">
         <v>6.62</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>4.13</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <v>35.39</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="34">
         <v>6.68</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="34">
         <v>4.47</v>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="34">
         <v>3.42</v>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="34">
         <v>7.65</v>
       </c>
-      <c r="I50" s="33">
+      <c r="I50" s="34">
         <v>11.77</v>
       </c>
-      <c r="J50" s="32"/>
-      <c r="K50" s="33">
+      <c r="J50" s="33"/>
+      <c r="K50" s="34">
         <v>5.91</v>
       </c>
-      <c r="L50" s="33">
+      <c r="L50" s="34">
         <v>4.75</v>
       </c>
-      <c r="M50" s="33">
+      <c r="M50" s="34">
         <v>5.73</v>
       </c>
-      <c r="N50" s="33">
+      <c r="N50" s="34">
         <v>3.0</v>
       </c>
-      <c r="O50" s="33">
+      <c r="O50" s="34">
         <v>2.9</v>
       </c>
-      <c r="P50" s="33">
+      <c r="P50" s="34">
         <v>4.23</v>
       </c>
-      <c r="Q50" s="33">
+      <c r="Q50" s="34">
         <v>7.89</v>
       </c>
-      <c r="R50" s="32"/>
-      <c r="S50" s="33">
+      <c r="R50" s="33"/>
+      <c r="S50" s="34">
         <v>5.29</v>
       </c>
-      <c r="T50" s="33">
+      <c r="T50" s="34">
         <v>6.02</v>
       </c>
-      <c r="U50" s="33">
+      <c r="U50" s="34">
         <v>8.17</v>
       </c>
-      <c r="V50" s="33">
+      <c r="V50" s="34">
         <v>3.81</v>
       </c>
-      <c r="W50" s="33">
+      <c r="W50" s="34">
         <v>4.03</v>
       </c>
-      <c r="X50" s="33">
+      <c r="X50" s="34">
         <v>4.67</v>
       </c>
-      <c r="Y50" s="32"/>
-      <c r="Z50" s="33">
+      <c r="Y50" s="33"/>
+      <c r="Z50" s="34">
         <v>9.14</v>
       </c>
-      <c r="AA50" s="33">
+      <c r="AA50" s="34">
         <v>14.43</v>
       </c>
-      <c r="AB50" s="33">
+      <c r="AB50" s="34">
         <v>11.53</v>
       </c>
-      <c r="AC50" s="33">
+      <c r="AC50" s="34">
         <v>9.92</v>
       </c>
-      <c r="AD50" s="33">
+      <c r="AD50" s="34">
         <v>8.37</v>
       </c>
-      <c r="AE50" s="32"/>
+      <c r="AE50" s="33"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
-        <v>454</v>
-      </c>
-      <c r="B51" s="33">
+      <c r="A51" s="31" t="s">
+        <v>455</v>
+      </c>
+      <c r="B51" s="34">
         <v>6.1</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="34">
         <v>5.5</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="34">
         <v>6.09</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="34">
         <v>5.53</v>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="34">
         <v>5.6</v>
       </c>
-      <c r="G51" s="33">
+      <c r="G51" s="34">
         <v>6.57</v>
       </c>
-      <c r="H51" s="33">
+      <c r="H51" s="34">
         <v>9.36</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="34">
         <v>9.11</v>
       </c>
-      <c r="J51" s="33">
+      <c r="J51" s="34">
         <v>5.9</v>
       </c>
-      <c r="K51" s="33">
+      <c r="K51" s="34">
         <v>3.91</v>
       </c>
-      <c r="L51" s="33">
+      <c r="L51" s="34">
         <v>3.8</v>
       </c>
-      <c r="M51" s="33">
+      <c r="M51" s="34">
         <v>4.12</v>
       </c>
-      <c r="N51" s="33">
+      <c r="N51" s="34">
         <v>4.75</v>
       </c>
-      <c r="O51" s="33">
+      <c r="O51" s="34">
         <v>5.38</v>
       </c>
-      <c r="P51" s="33">
+      <c r="P51" s="34">
         <v>6.6</v>
       </c>
-      <c r="Q51" s="33">
+      <c r="Q51" s="34">
         <v>7.71</v>
       </c>
-      <c r="R51" s="33">
+      <c r="R51" s="34">
         <v>7.02</v>
       </c>
-      <c r="S51" s="33">
+      <c r="S51" s="34">
         <v>5.8</v>
       </c>
-      <c r="T51" s="33">
+      <c r="T51" s="34">
         <v>5.73</v>
       </c>
-      <c r="U51" s="33">
+      <c r="U51" s="34">
         <v>6.96</v>
       </c>
-      <c r="V51" s="33">
+      <c r="V51" s="34">
         <v>7.2</v>
       </c>
-      <c r="W51" s="33">
+      <c r="W51" s="34">
         <v>10.08</v>
       </c>
-      <c r="X51" s="33">
+      <c r="X51" s="34">
         <v>11.92</v>
       </c>
-      <c r="Y51" s="33">
+      <c r="Y51" s="34">
         <v>12.5</v>
       </c>
-      <c r="Z51" s="33">
+      <c r="Z51" s="34">
         <v>10.67</v>
       </c>
-      <c r="AA51" s="32"/>
-      <c r="AB51" s="32"/>
-      <c r="AC51" s="32"/>
-      <c r="AD51" s="32"/>
-      <c r="AE51" s="32"/>
+      <c r="AA51" s="33"/>
+      <c r="AB51" s="33"/>
+      <c r="AC51" s="33"/>
+      <c r="AD51" s="33"/>
+      <c r="AE51" s="33"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="29"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29"/>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="29"/>
-      <c r="AA52" s="29"/>
-      <c r="AB52" s="29"/>
-      <c r="AC52" s="29"/>
-      <c r="AD52" s="29"/>
-      <c r="AE52" s="29"/>
+      <c r="A52" s="29" t="s">
+        <v>456</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
+      <c r="AD52" s="30"/>
+      <c r="AE52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
-        <v>456</v>
-      </c>
-      <c r="B53" s="33">
+      <c r="A53" s="31" t="s">
+        <v>457</v>
+      </c>
+      <c r="B53" s="34">
         <v>12.03</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="34">
         <v>4.55</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="32">
         <v>502.16</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="34">
         <v>7.34</v>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="34">
         <v>4.84</v>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="34">
         <v>3.91</v>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="34">
         <v>11.29</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="34">
         <v>23.38</v>
       </c>
-      <c r="J53" s="32"/>
-      <c r="K53" s="32"/>
-      <c r="L53" s="33">
+      <c r="J53" s="33"/>
+      <c r="K53" s="33"/>
+      <c r="L53" s="34">
         <v>16.43</v>
       </c>
-      <c r="M53" s="33">
+      <c r="M53" s="34">
         <v>34.21</v>
       </c>
-      <c r="N53" s="33">
+      <c r="N53" s="34">
         <v>5.07</v>
       </c>
-      <c r="O53" s="33">
+      <c r="O53" s="34">
         <v>3.96</v>
       </c>
-      <c r="P53" s="33">
+      <c r="P53" s="34">
         <v>6.19</v>
       </c>
-      <c r="Q53" s="32"/>
-      <c r="R53" s="32"/>
-      <c r="S53" s="32"/>
-      <c r="T53" s="33">
+      <c r="Q53" s="33"/>
+      <c r="R53" s="33"/>
+      <c r="S53" s="33"/>
+      <c r="T53" s="34">
         <v>10.33</v>
       </c>
-      <c r="U53" s="33">
+      <c r="U53" s="34">
         <v>15.4</v>
       </c>
-      <c r="V53" s="33">
+      <c r="V53" s="34">
         <v>10.51</v>
       </c>
-      <c r="W53" s="33">
+      <c r="W53" s="34">
         <v>8.9</v>
       </c>
-      <c r="X53" s="33">
+      <c r="X53" s="34">
         <v>12.27</v>
       </c>
-      <c r="Y53" s="32"/>
-      <c r="Z53" s="33">
+      <c r="Y53" s="33"/>
+      <c r="Z53" s="34">
         <v>18.4</v>
       </c>
-      <c r="AA53" s="33">
+      <c r="AA53" s="34">
         <v>23.51</v>
       </c>
-      <c r="AB53" s="33">
+      <c r="AB53" s="34">
         <v>18.32</v>
       </c>
-      <c r="AC53" s="33">
+      <c r="AC53" s="34">
         <v>15.04</v>
       </c>
-      <c r="AD53" s="33">
+      <c r="AD53" s="34">
         <v>13.63</v>
       </c>
-      <c r="AE53" s="32"/>
+      <c r="AE53" s="33"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
-        <v>457</v>
-      </c>
-      <c r="B54" s="33">
+      <c r="A54" s="31" t="s">
+        <v>458</v>
+      </c>
+      <c r="B54" s="34">
         <v>7.22</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="34">
         <v>6.22</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="34">
         <v>7.07</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <v>6.4</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <v>7.13</v>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="34">
         <v>11.8</v>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="34">
         <v>69.39</v>
       </c>
-      <c r="I54" s="32"/>
-      <c r="J54" s="33">
+      <c r="I54" s="33"/>
+      <c r="J54" s="34">
         <v>77.85</v>
       </c>
-      <c r="K54" s="33">
+      <c r="K54" s="34">
         <v>8.68</v>
       </c>
-      <c r="L54" s="33">
+      <c r="L54" s="34">
         <v>6.72</v>
       </c>
-      <c r="M54" s="33">
+      <c r="M54" s="34">
         <v>7.81</v>
       </c>
-      <c r="N54" s="33">
+      <c r="N54" s="34">
         <v>11.72</v>
       </c>
-      <c r="O54" s="33">
+      <c r="O54" s="34">
         <v>21.26</v>
       </c>
-      <c r="P54" s="33">
+      <c r="P54" s="34">
         <v>29.15</v>
       </c>
-      <c r="Q54" s="33">
+      <c r="Q54" s="34">
         <v>40.97</v>
       </c>
-      <c r="R54" s="33">
+      <c r="R54" s="34">
         <v>27.07</v>
       </c>
-      <c r="S54" s="33">
+      <c r="S54" s="34">
         <v>13.5</v>
       </c>
-      <c r="T54" s="33">
+      <c r="T54" s="34">
         <v>11.56</v>
       </c>
-      <c r="U54" s="33">
+      <c r="U54" s="34">
         <v>21.37</v>
       </c>
-      <c r="V54" s="33">
+      <c r="V54" s="34">
         <v>23.91</v>
       </c>
-      <c r="W54" s="33">
+      <c r="W54" s="34">
         <v>26.61</v>
       </c>
-      <c r="X54" s="33">
+      <c r="X54" s="34">
         <v>27.19</v>
       </c>
-      <c r="Y54" s="33">
+      <c r="Y54" s="34">
         <v>24.64</v>
       </c>
-      <c r="Z54" s="33">
+      <c r="Z54" s="34">
         <v>17.67</v>
       </c>
-      <c r="AA54" s="32"/>
-      <c r="AB54" s="32"/>
-      <c r="AC54" s="32"/>
-      <c r="AD54" s="32"/>
-      <c r="AE54" s="32"/>
+      <c r="AA54" s="33"/>
+      <c r="AB54" s="33"/>
+      <c r="AC54" s="33"/>
+      <c r="AD54" s="33"/>
+      <c r="AE54" s="33"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Y55" s="29"/>
-      <c r="Z55" s="29"/>
-      <c r="AA55" s="29"/>
-      <c r="AB55" s="29"/>
-      <c r="AC55" s="29"/>
-      <c r="AD55" s="29"/>
-      <c r="AE55" s="29"/>
+      <c r="A55" s="29" t="s">
+        <v>459</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="30"/>
+      <c r="AD55" s="30"/>
+      <c r="AE55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>459</v>
-      </c>
-      <c r="B56" s="33">
+      <c r="A56" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="B56" s="34">
         <v>3.61</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="34">
         <v>4.55</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <v>555.01</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="34">
         <v>6.83</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="34">
         <v>10.0</v>
       </c>
-      <c r="G56" s="33">
+      <c r="G56" s="34">
         <v>8.9</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <v>7.32</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="34">
         <v>27.19</v>
       </c>
-      <c r="J56" s="32"/>
-      <c r="K56" s="33">
+      <c r="J56" s="33"/>
+      <c r="K56" s="34">
         <v>28.2</v>
       </c>
-      <c r="L56" s="33">
+      <c r="L56" s="34">
         <v>8.08</v>
       </c>
-      <c r="M56" s="33">
+      <c r="M56" s="34">
         <v>10.37</v>
       </c>
-      <c r="N56" s="33">
+      <c r="N56" s="34">
         <v>4.58</v>
       </c>
-      <c r="O56" s="33">
+      <c r="O56" s="34">
         <v>3.96</v>
       </c>
-      <c r="P56" s="33">
+      <c r="P56" s="34">
         <v>5.36</v>
       </c>
-      <c r="Q56" s="33">
+      <c r="Q56" s="34">
         <v>25.04</v>
       </c>
-      <c r="R56" s="32"/>
-      <c r="S56" s="33">
+      <c r="R56" s="33"/>
+      <c r="S56" s="34">
         <v>19.54</v>
       </c>
-      <c r="T56" s="33">
+      <c r="T56" s="34">
         <v>10.33</v>
       </c>
-      <c r="U56" s="33">
+      <c r="U56" s="34">
         <v>15.4</v>
       </c>
-      <c r="V56" s="33">
+      <c r="V56" s="34">
         <v>10.51</v>
       </c>
-      <c r="W56" s="33">
+      <c r="W56" s="34">
         <v>8.9</v>
       </c>
-      <c r="X56" s="33">
+      <c r="X56" s="34">
         <v>12.27</v>
       </c>
-      <c r="Y56" s="32"/>
-      <c r="Z56" s="33">
+      <c r="Y56" s="33"/>
+      <c r="Z56" s="34">
         <v>12.39</v>
       </c>
-      <c r="AA56" s="33">
+      <c r="AA56" s="34">
         <v>16.04</v>
       </c>
-      <c r="AB56" s="33">
+      <c r="AB56" s="34">
         <v>11.83</v>
       </c>
-      <c r="AC56" s="32"/>
-      <c r="AD56" s="32"/>
-      <c r="AE56" s="32"/>
+      <c r="AC56" s="33"/>
+      <c r="AD56" s="33"/>
+      <c r="AE56" s="33"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>460</v>
-      </c>
-      <c r="B57" s="33">
+      <c r="A57" s="31" t="s">
+        <v>461</v>
+      </c>
+      <c r="B57" s="34">
         <v>1.23</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <v>1.35</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="34">
         <v>1.42</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="34">
         <v>1.51</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <v>1.25</v>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="34">
         <v>0.98</v>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="34">
         <v>0.84</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="34">
         <v>0.72</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="34">
         <v>0.58</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="34">
         <v>0.65</v>
       </c>
-      <c r="L57" s="33">
+      <c r="L57" s="34">
         <v>0.74</v>
       </c>
-      <c r="M57" s="33">
+      <c r="M57" s="34">
         <v>0.77</v>
       </c>
-      <c r="N57" s="33">
+      <c r="N57" s="34">
         <v>0.72</v>
       </c>
-      <c r="O57" s="33">
+      <c r="O57" s="34">
         <v>0.76</v>
       </c>
-      <c r="P57" s="33">
+      <c r="P57" s="34">
         <v>1.03</v>
       </c>
-      <c r="Q57" s="33">
+      <c r="Q57" s="34">
         <v>1.32</v>
       </c>
-      <c r="R57" s="33">
+      <c r="R57" s="34">
         <v>1.46</v>
       </c>
-      <c r="S57" s="33">
+      <c r="S57" s="34">
         <v>1.91</v>
       </c>
-      <c r="T57" s="33">
+      <c r="T57" s="34">
         <v>2.28</v>
       </c>
-      <c r="U57" s="33">
+      <c r="U57" s="34">
         <v>2.3</v>
       </c>
-      <c r="V57" s="33">
+      <c r="V57" s="34">
         <v>2.5</v>
       </c>
-      <c r="W57" s="33">
+      <c r="W57" s="34">
         <v>3.9</v>
       </c>
-      <c r="X57" s="33">
+      <c r="X57" s="34">
         <v>4.83</v>
       </c>
-      <c r="Y57" s="33">
+      <c r="Y57" s="34">
         <v>5.54</v>
       </c>
-      <c r="Z57" s="33">
+      <c r="Z57" s="34">
         <v>5.72</v>
       </c>
-      <c r="AA57" s="32"/>
-      <c r="AB57" s="32"/>
-      <c r="AC57" s="32"/>
-      <c r="AD57" s="32"/>
-      <c r="AE57" s="32"/>
+      <c r="AA57" s="33"/>
+      <c r="AB57" s="33"/>
+      <c r="AC57" s="33"/>
+      <c r="AD57" s="33"/>
+      <c r="AE57" s="33"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
-      <c r="V58" s="29"/>
-      <c r="W58" s="29"/>
-      <c r="X58" s="29"/>
-      <c r="Y58" s="29"/>
-      <c r="Z58" s="29"/>
-      <c r="AA58" s="29"/>
-      <c r="AB58" s="29"/>
-      <c r="AC58" s="29"/>
-      <c r="AD58" s="29"/>
-      <c r="AE58" s="29"/>
+      <c r="A58" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="30"/>
+      <c r="AD58" s="30"/>
+      <c r="AE58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>462</v>
-      </c>
-      <c r="B59" s="36">
+      <c r="A59" s="31" t="s">
+        <v>463</v>
+      </c>
+      <c r="B59" s="37">
         <v>-0.17</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <v>0.0</v>
       </c>
-      <c r="D59" s="36">
+      <c r="D59" s="37">
         <v>-5.06</v>
       </c>
-      <c r="E59" s="36">
+      <c r="E59" s="37">
         <v>-0.68</v>
       </c>
-      <c r="F59" s="33">
+      <c r="F59" s="34">
         <v>0.11</v>
       </c>
-      <c r="G59" s="33">
+      <c r="G59" s="34">
         <v>0.01</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <v>0.12</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="34">
         <v>0.16</v>
       </c>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="33">
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="34">
         <v>0.12</v>
       </c>
-      <c r="M59" s="36">
+      <c r="M59" s="37">
         <v>-0.4</v>
       </c>
-      <c r="N59" s="36">
+      <c r="N59" s="37">
         <v>-0.12</v>
       </c>
-      <c r="O59" s="33">
+      <c r="O59" s="34">
         <v>0.09</v>
       </c>
-      <c r="P59" s="33">
+      <c r="P59" s="34">
         <v>0.01</v>
       </c>
-      <c r="Q59" s="32"/>
-      <c r="R59" s="32"/>
-      <c r="S59" s="32"/>
-      <c r="T59" s="33">
+      <c r="Q59" s="33"/>
+      <c r="R59" s="33"/>
+      <c r="S59" s="33"/>
+      <c r="T59" s="34">
         <v>0.14</v>
       </c>
-      <c r="U59" s="33">
+      <c r="U59" s="34">
         <v>0.11</v>
       </c>
-      <c r="V59" s="36">
+      <c r="V59" s="37">
         <v>-0.38</v>
       </c>
-      <c r="W59" s="33">
+      <c r="W59" s="34">
         <v>0.16</v>
       </c>
-      <c r="X59" s="33">
+      <c r="X59" s="34">
         <v>0.08</v>
       </c>
-      <c r="Y59" s="32"/>
-      <c r="Z59" s="36">
+      <c r="Y59" s="33"/>
+      <c r="Z59" s="37">
         <v>-1.19</v>
       </c>
-      <c r="AA59" s="36">
+      <c r="AA59" s="37">
         <v>-1.66</v>
       </c>
-      <c r="AB59" s="36">
+      <c r="AB59" s="37">
         <v>-3.94</v>
       </c>
-      <c r="AC59" s="33">
+      <c r="AC59" s="34">
         <v>0.65</v>
       </c>
-      <c r="AD59" s="33">
+      <c r="AD59" s="34">
         <v>0.88</v>
       </c>
-      <c r="AE59" s="32"/>
+      <c r="AE59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
-        <v>463</v>
-      </c>
-      <c r="B60" s="36">
+      <c r="A60" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="B60" s="37">
         <v>-0.38</v>
       </c>
-      <c r="C60" s="33">
+      <c r="C60" s="34">
         <v>0.17</v>
       </c>
-      <c r="D60" s="36">
+      <c r="D60" s="37">
         <v>-0.18</v>
       </c>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="33">
+      <c r="E60" s="33"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="34">
         <v>0.2</v>
       </c>
-      <c r="H60" s="33">
+      <c r="H60" s="34">
         <v>1.55</v>
       </c>
-      <c r="I60" s="32"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="32"/>
-      <c r="L60" s="32"/>
-      <c r="M60" s="32"/>
-      <c r="N60" s="32"/>
-      <c r="O60" s="33">
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+      <c r="M60" s="33"/>
+      <c r="N60" s="33"/>
+      <c r="O60" s="34">
         <v>70.19</v>
       </c>
-      <c r="P60" s="33">
+      <c r="P60" s="34">
         <v>6.96</v>
       </c>
-      <c r="Q60" s="32"/>
-      <c r="R60" s="32"/>
-      <c r="S60" s="32"/>
-      <c r="T60" s="32"/>
-      <c r="U60" s="33">
+      <c r="Q60" s="33"/>
+      <c r="R60" s="33"/>
+      <c r="S60" s="33"/>
+      <c r="T60" s="33"/>
+      <c r="U60" s="34">
         <v>4.15</v>
       </c>
-      <c r="V60" s="36">
+      <c r="V60" s="37">
         <v>-1.65</v>
       </c>
-      <c r="W60" s="36">
+      <c r="W60" s="37">
         <v>-2.31</v>
       </c>
-      <c r="X60" s="36">
+      <c r="X60" s="37">
         <v>-1.37</v>
       </c>
-      <c r="Y60" s="32"/>
-      <c r="Z60" s="36">
+      <c r="Y60" s="33"/>
+      <c r="Z60" s="37">
         <v>-57.26</v>
       </c>
-      <c r="AA60" s="32"/>
-      <c r="AB60" s="32"/>
-      <c r="AC60" s="32"/>
-      <c r="AD60" s="32"/>
-      <c r="AE60" s="32"/>
+      <c r="AA60" s="33"/>
+      <c r="AB60" s="33"/>
+      <c r="AC60" s="33"/>
+      <c r="AD60" s="33"/>
+      <c r="AE60" s="33"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>464</v>
-      </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
-      <c r="W61" s="29"/>
-      <c r="X61" s="29"/>
-      <c r="Y61" s="29"/>
-      <c r="Z61" s="29"/>
-      <c r="AA61" s="29"/>
-      <c r="AB61" s="29"/>
-      <c r="AC61" s="29"/>
-      <c r="AD61" s="29"/>
-      <c r="AE61" s="29"/>
+      <c r="A61" s="29" t="s">
+        <v>465</v>
+      </c>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="30"/>
+      <c r="AD61" s="30"/>
+      <c r="AE61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>465</v>
-      </c>
-      <c r="B62" s="33">
+      <c r="A62" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="B62" s="34">
         <v>0.21</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <v>0.72</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="34">
         <v>0.53</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="34">
         <v>1.4</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <v>0.99</v>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="34">
         <v>0.57</v>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="34">
         <v>0.46</v>
       </c>
-      <c r="I62" s="33">
+      <c r="I62" s="34">
         <v>0.66</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J62" s="34">
         <v>0.2</v>
       </c>
-      <c r="K62" s="33">
+      <c r="K62" s="34">
         <v>0.17</v>
       </c>
-      <c r="L62" s="33">
+      <c r="L62" s="34">
         <v>0.27</v>
       </c>
-      <c r="M62" s="33">
+      <c r="M62" s="34">
         <v>0.29</v>
       </c>
-      <c r="N62" s="33">
+      <c r="N62" s="34">
         <v>0.25</v>
       </c>
-      <c r="O62" s="33">
+      <c r="O62" s="34">
         <v>0.29</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="34">
         <v>0.39</v>
       </c>
-      <c r="Q62" s="33">
+      <c r="Q62" s="34">
         <v>0.38</v>
       </c>
-      <c r="R62" s="33">
+      <c r="R62" s="34">
         <v>0.37</v>
       </c>
-      <c r="S62" s="33">
+      <c r="S62" s="34">
         <v>0.51</v>
       </c>
-      <c r="T62" s="33">
+      <c r="T62" s="34">
         <v>0.9</v>
       </c>
-      <c r="U62" s="33">
+      <c r="U62" s="34">
         <v>0.91</v>
       </c>
-      <c r="V62" s="33">
+      <c r="V62" s="34">
         <v>0.5</v>
       </c>
-      <c r="W62" s="33">
+      <c r="W62" s="34">
         <v>0.47</v>
       </c>
-      <c r="X62" s="33">
+      <c r="X62" s="34">
         <v>0.45</v>
       </c>
-      <c r="Y62" s="33">
+      <c r="Y62" s="34">
         <v>0.54</v>
       </c>
-      <c r="Z62" s="33">
+      <c r="Z62" s="34">
         <v>1.0</v>
       </c>
-      <c r="AA62" s="33">
+      <c r="AA62" s="34">
         <v>1.53</v>
       </c>
-      <c r="AB62" s="33">
+      <c r="AB62" s="34">
         <v>1.58</v>
       </c>
-      <c r="AC62" s="33">
+      <c r="AC62" s="34">
         <v>1.53</v>
       </c>
-      <c r="AD62" s="33">
+      <c r="AD62" s="34">
         <v>1.47</v>
       </c>
-      <c r="AE62" s="32"/>
+      <c r="AE62" s="33"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
-        <v>466</v>
-      </c>
-      <c r="B63" s="33">
+      <c r="A63" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="B63" s="34">
         <v>0.74</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="34">
         <v>0.84</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D63" s="34">
         <v>0.78</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="34">
         <v>0.81</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="34">
         <v>0.58</v>
       </c>
-      <c r="G63" s="33">
+      <c r="G63" s="34">
         <v>0.41</v>
       </c>
-      <c r="H63" s="33">
+      <c r="H63" s="34">
         <v>0.35</v>
       </c>
-      <c r="I63" s="33">
+      <c r="I63" s="34">
         <v>0.32</v>
       </c>
-      <c r="J63" s="33">
+      <c r="J63" s="34">
         <v>0.24</v>
       </c>
-      <c r="K63" s="33">
+      <c r="K63" s="34">
         <v>0.26</v>
       </c>
-      <c r="L63" s="33">
+      <c r="L63" s="34">
         <v>0.3</v>
       </c>
-      <c r="M63" s="33">
+      <c r="M63" s="34">
         <v>0.32</v>
       </c>
-      <c r="N63" s="33">
+      <c r="N63" s="34">
         <v>0.33</v>
       </c>
-      <c r="O63" s="33">
+      <c r="O63" s="34">
         <v>0.39</v>
       </c>
-      <c r="P63" s="33">
+      <c r="P63" s="34">
         <v>0.54</v>
       </c>
-      <c r="Q63" s="33">
+      <c r="Q63" s="34">
         <v>0.65</v>
       </c>
-      <c r="R63" s="33">
+      <c r="R63" s="34">
         <v>0.66</v>
       </c>
-      <c r="S63" s="33">
+      <c r="S63" s="34">
         <v>0.68</v>
       </c>
-      <c r="T63" s="33">
+      <c r="T63" s="34">
         <v>0.67</v>
       </c>
-      <c r="U63" s="33">
+      <c r="U63" s="34">
         <v>0.59</v>
       </c>
-      <c r="V63" s="33">
+      <c r="V63" s="34">
         <v>0.59</v>
       </c>
-      <c r="W63" s="33">
+      <c r="W63" s="34">
         <v>0.78</v>
       </c>
-      <c r="X63" s="33">
+      <c r="X63" s="34">
         <v>0.98</v>
       </c>
-      <c r="Y63" s="33">
+      <c r="Y63" s="34">
         <v>1.19</v>
       </c>
-      <c r="Z63" s="33">
+      <c r="Z63" s="34">
         <v>1.38</v>
       </c>
-      <c r="AA63" s="32"/>
-      <c r="AB63" s="32"/>
-      <c r="AC63" s="32"/>
-      <c r="AD63" s="32"/>
-      <c r="AE63" s="32"/>
+      <c r="AA63" s="33"/>
+      <c r="AB63" s="33"/>
+      <c r="AC63" s="33"/>
+      <c r="AD63" s="33"/>
+      <c r="AE63" s="33"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>467</v>
-      </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-      <c r="Z64" s="29"/>
-      <c r="AA64" s="29"/>
-      <c r="AB64" s="29"/>
-      <c r="AC64" s="29"/>
-      <c r="AD64" s="29"/>
-      <c r="AE64" s="29"/>
+      <c r="A64" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30"/>
+      <c r="AC64" s="30"/>
+      <c r="AD64" s="30"/>
+      <c r="AE64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="B65" s="33">
+      <c r="A65" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="B65" s="34">
         <v>1.79</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>3.89</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="34">
         <v>2.39</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="34">
         <v>4.95</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="34">
         <v>3.82</v>
       </c>
-      <c r="G65" s="33">
+      <c r="G65" s="34">
         <v>3.02</v>
       </c>
-      <c r="H65" s="33">
+      <c r="H65" s="34">
         <v>3.8</v>
       </c>
-      <c r="I65" s="33">
+      <c r="I65" s="34">
         <v>20.9</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J65" s="34">
         <v>16.08</v>
       </c>
-      <c r="K65" s="33">
+      <c r="K65" s="34">
         <v>3.18</v>
       </c>
-      <c r="L65" s="33">
+      <c r="L65" s="34">
         <v>2.83</v>
       </c>
-      <c r="M65" s="33">
+      <c r="M65" s="34">
         <v>3.38</v>
       </c>
-      <c r="N65" s="33">
+      <c r="N65" s="34">
         <v>2.06</v>
       </c>
-      <c r="O65" s="33">
+      <c r="O65" s="34">
         <v>1.73</v>
       </c>
-      <c r="P65" s="33">
+      <c r="P65" s="34">
         <v>2.43</v>
       </c>
-      <c r="Q65" s="32"/>
-      <c r="R65" s="33">
+      <c r="Q65" s="33"/>
+      <c r="R65" s="34">
         <v>15.39</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="34">
         <v>6.42</v>
       </c>
-      <c r="T65" s="33">
+      <c r="T65" s="34">
         <v>5.89</v>
       </c>
-      <c r="U65" s="33">
+      <c r="U65" s="34">
         <v>7.8</v>
       </c>
-      <c r="V65" s="33">
+      <c r="V65" s="34">
         <v>7.14</v>
       </c>
-      <c r="W65" s="33">
+      <c r="W65" s="34">
         <v>5.56</v>
       </c>
-      <c r="X65" s="33">
+      <c r="X65" s="34">
         <v>7.07</v>
       </c>
-      <c r="Y65" s="33">
+      <c r="Y65" s="34">
         <v>36.06</v>
       </c>
-      <c r="Z65" s="33">
+      <c r="Z65" s="34">
         <v>9.79</v>
       </c>
-      <c r="AA65" s="33">
+      <c r="AA65" s="34">
         <v>16.69</v>
       </c>
-      <c r="AB65" s="33">
+      <c r="AB65" s="34">
         <v>13.13</v>
       </c>
-      <c r="AC65" s="33">
+      <c r="AC65" s="34">
         <v>13.14</v>
       </c>
-      <c r="AD65" s="33">
+      <c r="AD65" s="34">
         <v>8.83</v>
       </c>
-      <c r="AE65" s="32"/>
+      <c r="AE65" s="33"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
-        <v>469</v>
-      </c>
-      <c r="B66" s="33">
+      <c r="A66" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="B66" s="34">
         <v>3.57</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="34">
         <v>3.71</v>
       </c>
-      <c r="D66" s="33">
+      <c r="D66" s="34">
         <v>3.69</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="34">
         <v>4.53</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="34">
         <v>4.54</v>
       </c>
-      <c r="G66" s="33">
+      <c r="G66" s="34">
         <v>4.81</v>
       </c>
-      <c r="H66" s="33">
+      <c r="H66" s="34">
         <v>5.25</v>
       </c>
-      <c r="I66" s="33">
+      <c r="I66" s="34">
         <v>5.32</v>
       </c>
-      <c r="J66" s="33">
+      <c r="J66" s="34">
         <v>3.11</v>
       </c>
-      <c r="K66" s="33">
+      <c r="K66" s="34">
         <v>2.4</v>
       </c>
-      <c r="L66" s="33">
+      <c r="L66" s="34">
         <v>2.35</v>
       </c>
-      <c r="M66" s="32"/>
-      <c r="N66" s="32"/>
-      <c r="O66" s="32"/>
-      <c r="P66" s="32"/>
-      <c r="Q66" s="32"/>
-      <c r="R66" s="33">
+      <c r="M66" s="33"/>
+      <c r="N66" s="33"/>
+      <c r="O66" s="33"/>
+      <c r="P66" s="33"/>
+      <c r="Q66" s="33"/>
+      <c r="R66" s="34">
         <v>7.04</v>
       </c>
-      <c r="S66" s="33">
+      <c r="S66" s="34">
         <v>6.51</v>
       </c>
-      <c r="T66" s="33">
+      <c r="T66" s="34">
         <v>6.58</v>
       </c>
-      <c r="U66" s="33">
+      <c r="U66" s="34">
         <v>7.98</v>
       </c>
-      <c r="V66" s="33">
+      <c r="V66" s="34">
         <v>8.59</v>
       </c>
-      <c r="W66" s="33">
+      <c r="W66" s="34">
         <v>10.7</v>
       </c>
-      <c r="X66" s="33">
+      <c r="X66" s="34">
         <v>12.79</v>
       </c>
-      <c r="Y66" s="33">
+      <c r="Y66" s="34">
         <v>13.83</v>
       </c>
-      <c r="Z66" s="33">
+      <c r="Z66" s="34">
         <v>12.24</v>
       </c>
-      <c r="AA66" s="32"/>
-      <c r="AB66" s="32"/>
-      <c r="AC66" s="32"/>
-      <c r="AD66" s="32"/>
-      <c r="AE66" s="32"/>
+      <c r="AA66" s="33"/>
+      <c r="AB66" s="33"/>
+      <c r="AC66" s="33"/>
+      <c r="AD66" s="33"/>
+      <c r="AE66" s="33"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>470</v>
-      </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="29"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
-      <c r="V67" s="29"/>
-      <c r="W67" s="29"/>
-      <c r="X67" s="29"/>
-      <c r="Y67" s="29"/>
-      <c r="Z67" s="29"/>
-      <c r="AA67" s="29"/>
-      <c r="AB67" s="29"/>
-      <c r="AC67" s="29"/>
-      <c r="AD67" s="29"/>
-      <c r="AE67" s="29"/>
+      <c r="A67" s="29" t="s">
+        <v>471</v>
+      </c>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+      <c r="AB67" s="30"/>
+      <c r="AC67" s="30"/>
+      <c r="AD67" s="30"/>
+      <c r="AE67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>471</v>
-      </c>
-      <c r="B68" s="33">
+      <c r="A68" s="31" t="s">
+        <v>472</v>
+      </c>
+      <c r="B68" s="34">
         <v>7.55</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="34">
         <v>1.92</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="34">
         <v>2.65</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <v>9.09</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <v>4.71</v>
       </c>
-      <c r="G68" s="33">
+      <c r="G68" s="34">
         <v>4.46</v>
       </c>
-      <c r="H68" s="33">
+      <c r="H68" s="34">
         <v>4.75</v>
       </c>
-      <c r="I68" s="33">
+      <c r="I68" s="34">
         <v>21.74</v>
       </c>
-      <c r="J68" s="32"/>
-      <c r="K68" s="33">
+      <c r="J68" s="33"/>
+      <c r="K68" s="34">
         <v>4.75</v>
       </c>
-      <c r="L68" s="33">
+      <c r="L68" s="34">
         <v>3.47</v>
       </c>
-      <c r="M68" s="33">
+      <c r="M68" s="34">
         <v>3.91</v>
       </c>
-      <c r="N68" s="33">
+      <c r="N68" s="34">
         <v>3.01</v>
       </c>
-      <c r="O68" s="33">
+      <c r="O68" s="34">
         <v>2.24</v>
       </c>
-      <c r="P68" s="33">
+      <c r="P68" s="34">
         <v>3.05</v>
       </c>
-      <c r="Q68" s="33">
+      <c r="Q68" s="34">
         <v>5.23</v>
       </c>
-      <c r="R68" s="33">
+      <c r="R68" s="34">
         <v>5.61</v>
       </c>
-      <c r="S68" s="33">
+      <c r="S68" s="34">
         <v>6.78</v>
       </c>
-      <c r="T68" s="33">
+      <c r="T68" s="34">
         <v>8.18</v>
       </c>
-      <c r="U68" s="33">
+      <c r="U68" s="34">
         <v>7.91</v>
       </c>
-      <c r="V68" s="33">
+      <c r="V68" s="34">
         <v>15.72</v>
       </c>
-      <c r="W68" s="33">
+      <c r="W68" s="34">
         <v>19.82</v>
       </c>
-      <c r="X68" s="33">
+      <c r="X68" s="34">
         <v>17.88</v>
       </c>
-      <c r="Y68" s="33">
+      <c r="Y68" s="34">
         <v>20.86</v>
       </c>
-      <c r="Z68" s="33">
+      <c r="Z68" s="34">
         <v>6.88</v>
       </c>
-      <c r="AA68" s="33">
+      <c r="AA68" s="34">
         <v>10.13</v>
       </c>
-      <c r="AB68" s="33">
+      <c r="AB68" s="34">
         <v>17.41</v>
       </c>
-      <c r="AC68" s="31">
+      <c r="AC68" s="32">
         <v>324.99</v>
       </c>
-      <c r="AD68" s="33">
+      <c r="AD68" s="34">
         <v>3.81</v>
       </c>
-      <c r="AE68" s="32"/>
+      <c r="AE68" s="33"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
-        <v>472</v>
-      </c>
-      <c r="B69" s="33">
+      <c r="A69" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="B69" s="34">
         <v>4.09</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="34">
         <v>4.02</v>
       </c>
-      <c r="D69" s="33">
+      <c r="D69" s="34">
         <v>5.03</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="34">
         <v>6.46</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="34">
         <v>6.11</v>
       </c>
-      <c r="G69" s="33">
+      <c r="G69" s="34">
         <v>6.97</v>
       </c>
-      <c r="H69" s="33">
+      <c r="H69" s="34">
         <v>7.12</v>
       </c>
-      <c r="I69" s="33">
+      <c r="I69" s="34">
         <v>7.11</v>
       </c>
-      <c r="J69" s="33">
+      <c r="J69" s="34">
         <v>4.38</v>
       </c>
-      <c r="K69" s="33">
+      <c r="K69" s="34">
         <v>3.14</v>
       </c>
-      <c r="L69" s="33">
+      <c r="L69" s="34">
         <v>3.01</v>
       </c>
-      <c r="M69" s="33">
+      <c r="M69" s="34">
         <v>3.24</v>
       </c>
-      <c r="N69" s="33">
+      <c r="N69" s="34">
         <v>3.47</v>
       </c>
-      <c r="O69" s="33">
+      <c r="O69" s="34">
         <v>4.19</v>
       </c>
-      <c r="P69" s="33">
+      <c r="P69" s="34">
         <v>5.94</v>
       </c>
-      <c r="Q69" s="33">
+      <c r="Q69" s="34">
         <v>7.17</v>
       </c>
-      <c r="R69" s="33">
+      <c r="R69" s="34">
         <v>8.01</v>
       </c>
-      <c r="S69" s="33">
+      <c r="S69" s="34">
         <v>9.04</v>
       </c>
-      <c r="T69" s="33">
+      <c r="T69" s="34">
         <v>10.12</v>
       </c>
-      <c r="U69" s="33">
+      <c r="U69" s="34">
         <v>12.35</v>
       </c>
-      <c r="V69" s="33">
+      <c r="V69" s="34">
         <v>11.76</v>
       </c>
-      <c r="W69" s="33">
+      <c r="W69" s="34">
         <v>10.76</v>
       </c>
-      <c r="X69" s="33">
+      <c r="X69" s="34">
         <v>11.22</v>
       </c>
-      <c r="Y69" s="33">
+      <c r="Y69" s="34">
         <v>13.23</v>
       </c>
-      <c r="Z69" s="33">
+      <c r="Z69" s="34">
         <v>9.89</v>
       </c>
-      <c r="AA69" s="32"/>
-      <c r="AB69" s="32"/>
-      <c r="AC69" s="32"/>
-      <c r="AD69" s="32"/>
-      <c r="AE69" s="32"/>
+      <c r="AA69" s="33"/>
+      <c r="AB69" s="33"/>
+      <c r="AC69" s="33"/>
+      <c r="AD69" s="33"/>
+      <c r="AE69" s="33"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
-        <v>473</v>
-      </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
-      <c r="Q70" s="29"/>
-      <c r="R70" s="29"/>
-      <c r="S70" s="29"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="29"/>
-      <c r="V70" s="29"/>
-      <c r="W70" s="29"/>
-      <c r="X70" s="29"/>
-      <c r="Y70" s="29"/>
-      <c r="Z70" s="29"/>
-      <c r="AA70" s="29"/>
-      <c r="AB70" s="29"/>
-      <c r="AC70" s="29"/>
-      <c r="AD70" s="29"/>
-      <c r="AE70" s="29"/>
+      <c r="A70" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
+      <c r="AA70" s="30"/>
+      <c r="AB70" s="30"/>
+      <c r="AC70" s="30"/>
+      <c r="AD70" s="30"/>
+      <c r="AE70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
-        <v>474</v>
-      </c>
-      <c r="B71" s="32"/>
-      <c r="C71" s="33">
+      <c r="A71" s="31" t="s">
+        <v>475</v>
+      </c>
+      <c r="B71" s="33"/>
+      <c r="C71" s="34">
         <v>2.0</v>
       </c>
-      <c r="D71" s="33">
+      <c r="D71" s="34">
         <v>2.99</v>
       </c>
-      <c r="E71" s="33">
+      <c r="E71" s="34">
         <v>10.91</v>
       </c>
-      <c r="F71" s="33">
+      <c r="F71" s="34">
         <v>5.14</v>
       </c>
-      <c r="G71" s="33">
+      <c r="G71" s="34">
         <v>5.09</v>
       </c>
-      <c r="H71" s="33">
+      <c r="H71" s="34">
         <v>6.24</v>
       </c>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="33">
+      <c r="I71" s="33"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="34">
         <v>6.73</v>
       </c>
-      <c r="L71" s="33">
+      <c r="L71" s="34">
         <v>5.09</v>
       </c>
-      <c r="M71" s="33">
+      <c r="M71" s="34">
         <v>5.81</v>
       </c>
-      <c r="N71" s="33">
+      <c r="N71" s="34">
         <v>4.31</v>
       </c>
-      <c r="O71" s="33">
+      <c r="O71" s="34">
         <v>2.49</v>
       </c>
-      <c r="P71" s="33">
+      <c r="P71" s="34">
         <v>3.26</v>
       </c>
-      <c r="Q71" s="33">
+      <c r="Q71" s="34">
         <v>7.76</v>
       </c>
-      <c r="R71" s="33">
+      <c r="R71" s="34">
         <v>61.55</v>
       </c>
-      <c r="S71" s="32"/>
-      <c r="T71" s="33">
+      <c r="S71" s="33"/>
+      <c r="T71" s="34">
         <v>19.05</v>
       </c>
-      <c r="U71" s="33">
+      <c r="U71" s="34">
         <v>12.81</v>
       </c>
-      <c r="V71" s="32"/>
-      <c r="W71" s="32"/>
-      <c r="X71" s="32"/>
-      <c r="Y71" s="32"/>
-      <c r="Z71" s="33">
+      <c r="V71" s="33"/>
+      <c r="W71" s="33"/>
+      <c r="X71" s="33"/>
+      <c r="Y71" s="33"/>
+      <c r="Z71" s="34">
         <v>13.84</v>
       </c>
-      <c r="AA71" s="33">
+      <c r="AA71" s="34">
         <v>49.24</v>
       </c>
-      <c r="AB71" s="32"/>
-      <c r="AC71" s="32"/>
-      <c r="AD71" s="33">
+      <c r="AB71" s="33"/>
+      <c r="AC71" s="33"/>
+      <c r="AD71" s="34">
         <v>4.28</v>
       </c>
-      <c r="AE71" s="32"/>
+      <c r="AE71" s="33"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="30" t="s">
-        <v>475</v>
-      </c>
-      <c r="B72" s="33">
+      <c r="A72" s="31" t="s">
+        <v>476</v>
+      </c>
+      <c r="B72" s="34">
         <v>4.74</v>
       </c>
-      <c r="C72" s="33">
+      <c r="C72" s="34">
         <v>4.42</v>
       </c>
-      <c r="D72" s="33">
+      <c r="D72" s="34">
         <v>5.81</v>
       </c>
-      <c r="E72" s="33">
+      <c r="E72" s="34">
         <v>7.92</v>
       </c>
-      <c r="F72" s="33">
+      <c r="F72" s="34">
         <v>7.74</v>
       </c>
-      <c r="G72" s="33">
+      <c r="G72" s="34">
         <v>10.2</v>
       </c>
-      <c r="H72" s="33">
+      <c r="H72" s="34">
         <v>12.29</v>
       </c>
-      <c r="I72" s="33">
+      <c r="I72" s="34">
         <v>13.63</v>
       </c>
-      <c r="J72" s="33">
+      <c r="J72" s="34">
         <v>6.76</v>
       </c>
-      <c r="K72" s="33">
+      <c r="K72" s="34">
         <v>4.13</v>
       </c>
-      <c r="L72" s="33">
+      <c r="L72" s="34">
         <v>3.72</v>
       </c>
-      <c r="M72" s="33">
+      <c r="M72" s="34">
         <v>4.0</v>
       </c>
-      <c r="N72" s="33">
+      <c r="N72" s="34">
         <v>4.75</v>
       </c>
-      <c r="O72" s="33">
+      <c r="O72" s="34">
         <v>7.42</v>
       </c>
-      <c r="P72" s="33">
+      <c r="P72" s="34">
         <v>13.64</v>
       </c>
-      <c r="Q72" s="33">
+      <c r="Q72" s="34">
         <v>19.73</v>
       </c>
-      <c r="R72" s="33">
+      <c r="R72" s="34">
         <v>57.31</v>
       </c>
-      <c r="S72" s="32"/>
-      <c r="T72" s="32"/>
-      <c r="U72" s="32"/>
-      <c r="V72" s="32"/>
-      <c r="W72" s="32"/>
-      <c r="X72" s="31">
+      <c r="S72" s="33"/>
+      <c r="T72" s="33"/>
+      <c r="U72" s="33"/>
+      <c r="V72" s="33"/>
+      <c r="W72" s="33"/>
+      <c r="X72" s="32">
         <v>116.88</v>
       </c>
-      <c r="Y72" s="33">
+      <c r="Y72" s="34">
         <v>81.24</v>
       </c>
-      <c r="Z72" s="33">
+      <c r="Z72" s="34">
         <v>22.82</v>
       </c>
-      <c r="AA72" s="32"/>
-      <c r="AB72" s="32"/>
-      <c r="AC72" s="32"/>
-      <c r="AD72" s="32"/>
-      <c r="AE72" s="32"/>
+      <c r="AA72" s="33"/>
+      <c r="AB72" s="33"/>
+      <c r="AC72" s="33"/>
+      <c r="AD72" s="33"/>
+      <c r="AE72" s="33"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
